--- a/Desafio 4 - Vale Refeição/Desafio 4 - Dados/DESLIGADOS MAIO - Seguir a regra.xlsx
+++ b/Desafio 4 - Vale Refeição/Desafio 4 - Dados/DESLIGADOS MAIO - Seguir a regra.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fe30ea445c4cf45e/Corporativo/I2A2/I2A2-Agentes Inteligentes com Redes Generativas/Dados Desafios/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Cursos e Treinamentos\Cientista de Dados\Treinamento Python\I2A2\Desafios\Desafio 4 - Vale Refeição\Desafio 4 - Dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{85B08DEA-6D41-4D41-97C8-FED50EA59017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D984402-6A75-4897-BA41-121E3287FD7A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC3C5A3B-0959-43DD-AFAD-6E19A6DF446B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1475C584-71FD-435B-B4EE-9C19DEBEC6B0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1475C584-71FD-435B-B4EE-9C19DEBEC6B0}"/>
   </bookViews>
   <sheets>
     <sheet name="DESLIGADOS " sheetId="1" r:id="rId1"/>
@@ -22,6 +22,9 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -458,15 +461,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82C6A81D-95CF-4A37-B9C3-5DE934ECBCD1}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:C52"/>
-  <sheetFormatPr defaultColWidth="52.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="52.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.21875" customWidth="1"/>
-    <col min="2" max="2" width="21.6640625" customWidth="1"/>
-    <col min="3" max="3" width="33.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" customWidth="1"/>
+    <col min="3" max="3" width="33.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -477,7 +481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>34706</v>
       </c>
@@ -488,7 +492,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>31486</v>
       </c>
@@ -499,7 +503,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>34641</v>
       </c>
@@ -510,7 +514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>26139</v>
       </c>
@@ -521,7 +525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>34179</v>
       </c>
@@ -532,7 +536,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>33482</v>
       </c>
@@ -543,7 +547,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>33492</v>
       </c>
@@ -552,7 +556,7 @@
       </c>
       <c r="C8" s="5"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>33627</v>
       </c>
@@ -563,7 +567,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>33404</v>
       </c>
@@ -574,7 +578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>33922</v>
       </c>
@@ -585,7 +589,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>25707</v>
       </c>
@@ -596,7 +600,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>34935</v>
       </c>
@@ -607,7 +611,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>33989</v>
       </c>
@@ -618,7 +622,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>29294</v>
       </c>
@@ -629,7 +633,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>31394</v>
       </c>
@@ -640,7 +644,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>25670</v>
       </c>
@@ -651,7 +655,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>34387</v>
       </c>
@@ -662,7 +666,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>33711</v>
       </c>
@@ -673,7 +677,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>34819</v>
       </c>
@@ -684,7 +688,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>35474</v>
       </c>
@@ -695,7 +699,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>33835</v>
       </c>
@@ -706,7 +710,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>35161</v>
       </c>
@@ -717,7 +721,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>35270</v>
       </c>
@@ -728,7 +732,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>31019</v>
       </c>
@@ -739,7 +743,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>31889</v>
       </c>
@@ -750,7 +754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>35575</v>
       </c>
@@ -761,7 +765,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>34721</v>
       </c>
@@ -772,7 +776,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>35554</v>
       </c>
@@ -783,7 +787,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>35569</v>
       </c>
@@ -794,7 +798,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>31880</v>
       </c>
@@ -805,7 +809,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>34841</v>
       </c>
@@ -816,7 +820,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>34534</v>
       </c>
@@ -825,7 +829,7 @@
       </c>
       <c r="C33" s="5"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>35664</v>
       </c>
@@ -836,7 +840,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>35589</v>
       </c>
@@ -847,7 +851,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>32946</v>
       </c>
@@ -858,7 +862,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>27226</v>
       </c>
@@ -869,7 +873,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>34417</v>
       </c>
@@ -880,7 +884,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>34924</v>
       </c>
@@ -891,7 +895,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>33417</v>
       </c>
@@ -902,7 +906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>34477</v>
       </c>
@@ -911,7 +915,7 @@
       </c>
       <c r="C41" s="5"/>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>34884</v>
       </c>
@@ -922,7 +926,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>35558</v>
       </c>
@@ -933,7 +937,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>30130</v>
       </c>
@@ -944,7 +948,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>32636</v>
       </c>
@@ -955,7 +959,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>35564</v>
       </c>
@@ -966,7 +970,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>30673</v>
       </c>
@@ -977,7 +981,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>35162</v>
       </c>
@@ -988,7 +992,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>33428</v>
       </c>
@@ -999,7 +1003,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>31314</v>
       </c>
@@ -1008,7 +1012,7 @@
       </c>
       <c r="C50" s="5"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>34785</v>
       </c>
@@ -1019,7 +1023,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>32533</v>
       </c>
@@ -1031,7 +1035,17 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C52" xr:uid="{82C6A81D-95CF-4A37-B9C3-5DE934ECBCD1}"/>
+  <autoFilter ref="A1:C52" xr:uid="{82C6A81D-95CF-4A37-B9C3-5DE934ECBCD1}">
+    <filterColumn colId="1">
+      <filters>
+        <dateGroupItem year="2025" month="5" day="16" dateTimeGrouping="day"/>
+        <dateGroupItem year="2025" month="5" day="17" dateTimeGrouping="day"/>
+        <dateGroupItem year="2025" month="5" day="18" dateTimeGrouping="day"/>
+        <dateGroupItem year="2025" month="5" day="27" dateTimeGrouping="day"/>
+        <dateGroupItem year="2025" month="5" day="29" dateTimeGrouping="day"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Calibri"&amp;10&amp;KFF0000 Classificação: Restrito&amp;1#_x000D_</oddHeader>
